--- a/exports/trend_1d/ABCAPITAL_full_report.xlsx
+++ b/exports/trend_1d/ABCAPITAL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>16.2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43082</v>
+        <v>43083</v>
       </c>
       <c r="H2" t="n">
-        <v>184.8</v>
+        <v>182.85</v>
       </c>
       <c r="I2" t="n">
         <v>184.0694704913767</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K2" t="n">
-        <v>-9.08</v>
+        <v>-10.04</v>
       </c>
       <c r="L2" t="n">
         <v>14.64</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.09</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43196</v>
+        <v>43199</v>
       </c>
       <c r="H3" t="n">
-        <v>157</v>
+        <v>159.15</v>
       </c>
       <c r="I3" t="n">
         <v>157.5920872844652</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K3" t="n">
-        <v>14.14</v>
+        <v>12.96</v>
       </c>
       <c r="L3" t="n">
         <v>5.17</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H4" t="n">
-        <v>151.4</v>
+        <v>149.95</v>
       </c>
       <c r="I4" t="n">
         <v>150.1118548949433</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.87</v>
+        <v>-5.78</v>
       </c>
       <c r="L4" t="n">
-        <v>5.31</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>0.63</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H5" t="n">
-        <v>129.85</v>
+        <v>140</v>
       </c>
       <c r="I5" t="n">
         <v>135.0958697718308</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K5" t="n">
-        <v>13.4</v>
+        <v>6.64</v>
       </c>
       <c r="L5" t="n">
         <v>1.9</v>
@@ -726,7 +785,7 @@
         <v>1.53</v>
       </c>
       <c r="N5" t="n">
-        <v>4.18</v>
+        <v>7.82</v>
       </c>
       <c r="O5" t="n">
         <v>-0.96</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.2</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43340</v>
+        <v>43341</v>
       </c>
       <c r="H6" t="n">
-        <v>138.2</v>
+        <v>137.3</v>
       </c>
       <c r="I6" t="n">
         <v>137.9028986154604</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.29</v>
+        <v>-1.93</v>
       </c>
       <c r="L6" t="n">
         <v>6.89</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.81</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43418</v>
+        <v>43419</v>
       </c>
       <c r="H7" t="n">
-        <v>107.3</v>
+        <v>110.4</v>
       </c>
       <c r="I7" t="n">
         <v>108.6121567176231</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" t="n">
-        <v>21.85</v>
+        <v>19.59</v>
       </c>
       <c r="L7" t="n">
         <v>5.61</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>12.43</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43434</v>
+        <v>43437</v>
       </c>
       <c r="H8" t="n">
-        <v>105.05</v>
+        <v>101.9</v>
       </c>
       <c r="I8" t="n">
         <v>103.274438541574</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.85</v>
+        <v>-7.7</v>
       </c>
       <c r="L8" t="n">
-        <v>6.52</v>
+        <v>8.24</v>
       </c>
       <c r="M8" t="n">
         <v>0.43</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.95</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43517</v>
+        <v>43518</v>
       </c>
       <c r="H9" t="n">
-        <v>81.95</v>
+        <v>86.8</v>
       </c>
       <c r="I9" t="n">
         <v>85.72596531159341</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K9" t="n">
-        <v>19.58</v>
+        <v>14.82</v>
       </c>
       <c r="L9" t="n">
         <v>3.93</v>
@@ -954,7 +1061,7 @@
         <v>2.48</v>
       </c>
       <c r="N9" t="n">
-        <v>3.58</v>
+        <v>5.92</v>
       </c>
       <c r="O9" t="n">
         <v>-3</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.97</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43598</v>
+        <v>43599</v>
       </c>
       <c r="H10" t="n">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>94.43433763756346</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K10" t="n">
-        <v>9.449999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="L10" t="n">
         <v>6.05</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H11" t="n">
-        <v>97.59999999999999</v>
+        <v>102.75</v>
       </c>
       <c r="I11" t="n">
         <v>99.88763684187592</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.39</v>
+        <v>-8.85</v>
       </c>
       <c r="L11" t="n">
-        <v>4.34</v>
+        <v>9.85</v>
       </c>
       <c r="M11" t="n">
         <v>3.47</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>5.28</v>
       </c>
       <c r="O11" t="n">
         <v>-0.63</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>11.23</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43629</v>
+        <v>43630</v>
       </c>
       <c r="H12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I12" t="n">
         <v>94.85079653745248</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.54</v>
+        <v>-8.52</v>
       </c>
       <c r="L12" t="n">
-        <v>8.27</v>
+        <v>8.76</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.83</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43693</v>
+        <v>43696</v>
       </c>
       <c r="H13" t="n">
-        <v>87.84999999999999</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>90.29426382775335</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K13" t="n">
-        <v>6.54</v>
+        <v>3.56</v>
       </c>
       <c r="L13" t="n">
         <v>1.81</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>12.55</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43735</v>
+        <v>43738</v>
       </c>
       <c r="H14" t="n">
-        <v>89.7</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>88.11397217525138</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.05</v>
+        <v>-6.4</v>
       </c>
       <c r="L14" t="n">
-        <v>6.51</v>
+        <v>6.73</v>
       </c>
       <c r="M14" t="n">
         <v>2.02</v>
       </c>
       <c r="N14" t="n">
-        <v>2.52</v>
+        <v>5.41</v>
       </c>
       <c r="O14" t="n">
         <v>3.19</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>15.73</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43776</v>
+        <v>43777</v>
       </c>
       <c r="H15" t="n">
-        <v>84.7</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>85.80016014255415</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K15" t="n">
-        <v>0.18</v>
+        <v>-2.36</v>
       </c>
       <c r="L15" t="n">
         <v>5.83</v>
       </c>
       <c r="M15" t="n">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
         <v>4.47</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.08</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43808</v>
+        <v>43809</v>
       </c>
       <c r="H16" t="n">
-        <v>96.34999999999999</v>
+        <v>91.95</v>
       </c>
       <c r="I16" t="n">
         <v>94.04023161837281</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K16" t="n">
-        <v>10.94</v>
+        <v>5.87</v>
       </c>
       <c r="L16" t="n">
         <v>9.039999999999999</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>21.74</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43839</v>
+        <v>43840</v>
       </c>
       <c r="H17" t="n">
-        <v>105.5</v>
+        <v>109.05</v>
       </c>
       <c r="I17" t="n">
         <v>108.3140830573189</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K17" t="n">
-        <v>-14.74</v>
+        <v>-18.6</v>
       </c>
       <c r="L17" t="n">
-        <v>19.36</v>
+        <v>22.19</v>
       </c>
       <c r="M17" t="n">
         <v>4.38</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>13.27</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H18" t="n">
-        <v>99.2</v>
+        <v>95.05</v>
       </c>
       <c r="I18" t="n">
         <v>97.83527667673199</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>-9.029999999999999</v>
+        <v>-12.84</v>
       </c>
       <c r="L18" t="n">
-        <v>9.67</v>
+        <v>13.89</v>
       </c>
       <c r="M18" t="n">
         <v>2.15</v>
       </c>
       <c r="N18" t="n">
-        <v>1.95</v>
+        <v>4.18</v>
       </c>
       <c r="O18" t="n">
         <v>3.36</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>16.65</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H19" t="n">
-        <v>46.8</v>
+        <v>51.15</v>
       </c>
       <c r="I19" t="n">
         <v>49.80234441818985</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K19" t="n">
-        <v>50.76</v>
+        <v>46.19</v>
       </c>
       <c r="L19" t="n">
         <v>7.42</v>
@@ -1524,7 +1751,7 @@
         <v>9.66</v>
       </c>
       <c r="N19" t="n">
-        <v>8.949999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>-4.18</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>19.47</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44041</v>
+        <v>44042</v>
       </c>
       <c r="H20" t="n">
-        <v>56.7</v>
+        <v>55.5</v>
       </c>
       <c r="I20" t="n">
         <v>55.72343879036595</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K20" t="n">
-        <v>10.85</v>
+        <v>8.5</v>
       </c>
       <c r="L20" t="n">
         <v>8.9</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>14.05</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44061</v>
+        <v>44062</v>
       </c>
       <c r="H21" t="n">
-        <v>59.9</v>
+        <v>61.55</v>
       </c>
       <c r="I21" t="n">
         <v>61.26220818044689</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.93</v>
+        <v>-10.9</v>
       </c>
       <c r="L21" t="n">
-        <v>11.17</v>
+        <v>12.34</v>
       </c>
       <c r="M21" t="n">
         <v>1.69</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.95</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H22" t="n">
-        <v>63.15</v>
+        <v>61.35</v>
       </c>
       <c r="I22" t="n">
         <v>62.51615645875759</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6</v>
+        <v>-0.32</v>
       </c>
       <c r="L22" t="n">
         <v>5.69</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>18.15</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44124</v>
+        <v>44125</v>
       </c>
       <c r="H23" t="n">
-        <v>62.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>67.28144349972042</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.22</v>
+        <v>-11</v>
       </c>
       <c r="L23" t="n">
-        <v>7.01</v>
+        <v>12.47</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>2.78</v>
+        <v>9.66</v>
       </c>
       <c r="O23" t="n">
         <v>-2.85</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>15.59</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H24" t="n">
-        <v>88.90000000000001</v>
+        <v>80.75</v>
       </c>
       <c r="I24" t="n">
         <v>83.11944264187235</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K24" t="n">
-        <v>30.54</v>
+        <v>18.58</v>
       </c>
       <c r="L24" t="n">
         <v>8.74</v>
@@ -1809,7 +2096,7 @@
         <v>2.57</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>9.17</v>
       </c>
       <c r="O24" t="n">
         <v>9.66</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>18.99</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44202</v>
+        <v>44203</v>
       </c>
       <c r="H25" t="n">
-        <v>88.55</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>92.78413458055337</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>-9.66</v>
+        <v>-15.05</v>
       </c>
       <c r="L25" t="n">
-        <v>13.31</v>
+        <v>15.79</v>
       </c>
       <c r="M25" t="n">
         <v>0.99</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>14.57</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H26" t="n">
-        <v>84.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>81.58417187642493</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K26" t="n">
-        <v>-9.470000000000001</v>
+        <v>-13.46</v>
       </c>
       <c r="L26" t="n">
-        <v>9.85</v>
+        <v>13.89</v>
       </c>
       <c r="M26" t="n">
         <v>0.77</v>
       </c>
       <c r="N26" t="n">
-        <v>3.91</v>
+        <v>4.4</v>
       </c>
       <c r="O26" t="n">
         <v>4.91</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>16.24</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44239</v>
+        <v>44242</v>
       </c>
       <c r="H27" t="n">
-        <v>88.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I27" t="n">
         <v>92.37912749759077</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K27" t="n">
-        <v>-10.32</v>
+        <v>-17.04</v>
       </c>
       <c r="L27" t="n">
-        <v>15.3</v>
+        <v>18.16</v>
       </c>
       <c r="M27" t="n">
         <v>1.55</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>13.64</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44309</v>
+        <v>44312</v>
       </c>
       <c r="H28" t="n">
-        <v>116.1</v>
+        <v>113.05</v>
       </c>
       <c r="I28" t="n">
         <v>113.3932526466615</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K28" t="n">
-        <v>23.38</v>
+        <v>20.14</v>
       </c>
       <c r="L28" t="n">
         <v>4.78</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.2</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44462</v>
+        <v>44463</v>
       </c>
       <c r="H29" t="n">
-        <v>113.1</v>
+        <v>115.45</v>
       </c>
       <c r="I29" t="n">
         <v>115.3765991976873</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.04</v>
+        <v>-2.12</v>
       </c>
       <c r="L29" t="n">
         <v>15.75</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>9.93</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H30" t="n">
-        <v>106.3</v>
+        <v>103.75</v>
       </c>
       <c r="I30" t="n">
         <v>105.5072811680699</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.93</v>
+        <v>-10.13</v>
       </c>
       <c r="L30" t="n">
-        <v>8.19</v>
+        <v>10.65</v>
       </c>
       <c r="M30" t="n">
         <v>0.49</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.43</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44504</v>
+        <v>44508</v>
       </c>
       <c r="H31" t="n">
-        <v>105.4</v>
+        <v>107.2</v>
       </c>
       <c r="I31" t="n">
         <v>106.8643148548055</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.59</v>
+        <v>-3.33</v>
       </c>
       <c r="L31" t="n">
         <v>4.92</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>12.69</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H32" t="n">
-        <v>116.6</v>
+        <v>111.3</v>
       </c>
       <c r="I32" t="n">
         <v>112.6662530868893</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K32" t="n">
-        <v>8.77</v>
+        <v>3.82</v>
       </c>
       <c r="L32" t="n">
         <v>7.65</v>
       </c>
       <c r="M32" t="n">
-        <v>0.84</v>
+        <v>2.27</v>
       </c>
       <c r="N32" t="n">
-        <v>3.52</v>
+        <v>4.55</v>
       </c>
       <c r="O32" t="n">
         <v>1.71</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>13.4</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H33" t="n">
-        <v>123.9</v>
+        <v>129.55</v>
       </c>
       <c r="I33" t="n">
         <v>126.2146202147227</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>-11.32</v>
+        <v>-16.4</v>
       </c>
       <c r="L33" t="n">
-        <v>12.76</v>
+        <v>17.21</v>
       </c>
       <c r="M33" t="n">
         <v>1.19</v>
       </c>
       <c r="N33" t="n">
-        <v>3.34</v>
+        <v>4.56</v>
       </c>
       <c r="O33" t="n">
         <v>-4.55</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>12.64</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H34" t="n">
-        <v>123.3</v>
+        <v>114.9</v>
       </c>
       <c r="I34" t="n">
         <v>121.1328056142819</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.82</v>
+        <v>-11.31</v>
       </c>
       <c r="L34" t="n">
-        <v>6.18</v>
+        <v>12.62</v>
       </c>
       <c r="M34" t="n">
         <v>1.47</v>
       </c>
       <c r="N34" t="n">
-        <v>3.48</v>
+        <v>6.81</v>
       </c>
       <c r="O34" t="n">
         <v>4.56</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>17.7</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44659</v>
+        <v>44662</v>
       </c>
       <c r="H35" t="n">
-        <v>113.55</v>
+        <v>116.35</v>
       </c>
       <c r="I35" t="n">
         <v>114.1975881212559</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K35" t="n">
-        <v>1.17</v>
+        <v>-1.26</v>
       </c>
       <c r="L35" t="n">
         <v>12.53</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>9.09</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H36" t="n">
-        <v>110.9</v>
+        <v>106.7</v>
       </c>
       <c r="I36" t="n">
         <v>109.4395982840314</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.68</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>7.61</v>
+        <v>9.5</v>
       </c>
       <c r="M36" t="n">
         <v>1.93</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>14.2</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44762</v>
+        <v>44763</v>
       </c>
       <c r="H37" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
         <v>98.45912640230478</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K37" t="n">
-        <v>10.03</v>
+        <v>6.28</v>
       </c>
       <c r="L37" t="n">
         <v>2.91</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H38" t="n">
-        <v>111.85</v>
+        <v>107.65</v>
       </c>
       <c r="I38" t="n">
         <v>110.8900468743558</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K38" t="n">
-        <v>11.85</v>
+        <v>7.65</v>
       </c>
       <c r="L38" t="n">
         <v>3.85</v>
@@ -2607,7 +3062,7 @@
         <v>4.82</v>
       </c>
       <c r="N38" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="O38" t="n">
         <v>4.17</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>11.88</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44867</v>
+        <v>44868</v>
       </c>
       <c r="H39" t="n">
-        <v>117.95</v>
+        <v>119.75</v>
       </c>
       <c r="I39" t="n">
         <v>118.7884494267042</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K39" t="n">
-        <v>-9.57</v>
+        <v>-11.24</v>
       </c>
       <c r="L39" t="n">
-        <v>11.38</v>
+        <v>11.7</v>
       </c>
       <c r="M39" t="n">
         <v>1.94</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.41</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H40" t="n">
-        <v>147.85</v>
+        <v>143.35</v>
       </c>
       <c r="I40" t="n">
         <v>146.4430025445664</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K40" t="n">
-        <v>23.47</v>
+        <v>19.71</v>
       </c>
       <c r="L40" t="n">
         <v>2.71</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.6</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H41" t="n">
-        <v>145.6</v>
+        <v>148.4</v>
       </c>
       <c r="I41" t="n">
         <v>148.2723964916144</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.57</v>
+        <v>-3.52</v>
       </c>
       <c r="L41" t="n">
         <v>10.08</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.32</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44998</v>
+        <v>44999</v>
       </c>
       <c r="H42" t="n">
-        <v>147.05</v>
+        <v>144.95</v>
       </c>
       <c r="I42" t="n">
         <v>146.0978038610831</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.91</v>
+        <v>-2.32</v>
       </c>
       <c r="L42" t="n">
         <v>7.68</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.34</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45022</v>
+        <v>45026</v>
       </c>
       <c r="H43" t="n">
-        <v>157.9</v>
+        <v>159.75</v>
       </c>
       <c r="I43" t="n">
         <v>158.4913759852704</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.93</v>
+        <v>-10.21</v>
       </c>
       <c r="L43" t="n">
-        <v>9.9</v>
+        <v>10.59</v>
       </c>
       <c r="M43" t="n">
         <v>1</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.53</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45149</v>
+        <v>45152</v>
       </c>
       <c r="H44" t="n">
-        <v>183.55</v>
+        <v>182.65</v>
       </c>
       <c r="I44" t="n">
         <v>183.4208204801384</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K44" t="n">
-        <v>14.9</v>
+        <v>14.33</v>
       </c>
       <c r="L44" t="n">
         <v>2.75</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.59</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45294</v>
+        <v>45295</v>
       </c>
       <c r="H45" t="n">
-        <v>170.4</v>
+        <v>174.1</v>
       </c>
       <c r="I45" t="n">
         <v>170.7874137275782</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K45" t="n">
-        <v>6.71</v>
+        <v>4.68</v>
       </c>
       <c r="L45" t="n">
         <v>5.37</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>6</v>
+      </c>
+      <c r="U45" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.09</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H46" t="n">
-        <v>174.1</v>
+        <v>163.5</v>
       </c>
       <c r="I46" t="n">
         <v>166.7491706660797</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>-6.09</v>
       </c>
       <c r="L46" t="n">
-        <v>2.01</v>
+        <v>6.55</v>
       </c>
       <c r="M46" t="n">
         <v>1.17</v>
       </c>
       <c r="N46" t="n">
-        <v>2.23</v>
+        <v>6.09</v>
       </c>
       <c r="O46" t="n">
         <v>2.17</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>12.39</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="H47" t="n">
-        <v>166.85</v>
+        <v>180.35</v>
       </c>
       <c r="I47" t="n">
         <v>178.4106856528432</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.05</v>
+        <v>-10.31</v>
       </c>
       <c r="L47" t="n">
-        <v>7.22</v>
+        <v>13.39</v>
       </c>
       <c r="M47" t="n">
-        <v>0.68</v>
+        <v>1.29</v>
       </c>
       <c r="N47" t="n">
-        <v>1.57</v>
+        <v>8.09</v>
       </c>
       <c r="O47" t="n">
         <v>-6.09</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>12.05</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H48" t="n">
-        <v>183.7</v>
+        <v>171.4</v>
       </c>
       <c r="I48" t="n">
         <v>173.7326371736972</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K48" t="n">
-        <v>1.86</v>
+        <v>-4.96</v>
       </c>
       <c r="L48" t="n">
         <v>6.29</v>
@@ -3177,7 +3752,7 @@
         <v>1.14</v>
       </c>
       <c r="N48" t="n">
-        <v>5.76</v>
+        <v>6.7</v>
       </c>
       <c r="O48" t="n">
         <v>8.09</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>17.1</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H49" t="n">
-        <v>181.85</v>
+        <v>201.05</v>
       </c>
       <c r="I49" t="n">
         <v>189.1950098750885</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.1</v>
+        <v>-17.3</v>
       </c>
       <c r="L49" t="n">
-        <v>7.41</v>
+        <v>19.31</v>
       </c>
       <c r="M49" t="n">
-        <v>1.45</v>
+        <v>3.38</v>
       </c>
       <c r="N49" t="n">
-        <v>3.68</v>
+        <v>10.56</v>
       </c>
       <c r="O49" t="n">
         <v>-6.7</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>13.81</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H50" t="n">
-        <v>229.55</v>
+        <v>206.1</v>
       </c>
       <c r="I50" t="n">
         <v>209.48994380276</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K50" t="n">
-        <v>14.18</v>
+        <v>2.51</v>
       </c>
       <c r="L50" t="n">
         <v>7.49</v>
@@ -3291,7 +3890,7 @@
         <v>1.21</v>
       </c>
       <c r="N50" t="n">
-        <v>3.88</v>
+        <v>10.22</v>
       </c>
       <c r="O50" t="n">
         <v>10.56</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>17.4</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45462</v>
+        <v>45463</v>
       </c>
       <c r="H51" t="n">
-        <v>238.1</v>
+        <v>243.02</v>
       </c>
       <c r="I51" t="n">
         <v>241.966550577516</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K51" t="n">
-        <v>-15.53</v>
+        <v>-17.91</v>
       </c>
       <c r="L51" t="n">
-        <v>18.05</v>
+        <v>19.8</v>
       </c>
       <c r="M51" t="n">
         <v>1.31</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>11.84</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H52" t="n">
-        <v>222.73</v>
+        <v>215.64</v>
       </c>
       <c r="I52" t="n">
         <v>217.9869068626418</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K52" t="n">
-        <v>-8.35</v>
+        <v>-11.27</v>
       </c>
       <c r="L52" t="n">
-        <v>8.81</v>
+        <v>11.51</v>
       </c>
       <c r="M52" t="n">
         <v>0.67</v>
       </c>
       <c r="N52" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="O52" t="n">
         <v>2.07</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45534</v>
+        <v>45537</v>
       </c>
       <c r="H53" t="n">
-        <v>220.11</v>
+        <v>226.96</v>
       </c>
       <c r="I53" t="n">
         <v>226.6233740211386</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.07</v>
+        <v>-5.25</v>
       </c>
       <c r="L53" t="n">
         <v>6.38</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.65</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45575</v>
+        <v>45576</v>
       </c>
       <c r="H54" t="n">
-        <v>224.39</v>
+        <v>220.84</v>
       </c>
       <c r="I54" t="n">
         <v>221.2391685981209</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.13</v>
+        <v>-2.7</v>
       </c>
       <c r="L54" t="n">
         <v>6.24</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H55" t="n">
-        <v>166.49</v>
+        <v>170.79</v>
       </c>
       <c r="I55" t="n">
         <v>170.154557108968</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K55" t="n">
-        <v>24.61</v>
+        <v>22.66</v>
       </c>
       <c r="L55" t="n">
         <v>3.29</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>6</v>
+      </c>
+      <c r="U55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.09</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H56" t="n">
-        <v>260.35</v>
+        <v>253.75</v>
       </c>
       <c r="I56" t="n">
         <v>256.5384035755</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K56" t="n">
-        <v>52.44</v>
+        <v>48.57</v>
       </c>
       <c r="L56" t="n">
         <v>2.66</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>9.48</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45870</v>
+        <v>45873</v>
       </c>
       <c r="H57" t="n">
-        <v>251.45</v>
+        <v>278.45</v>
       </c>
       <c r="I57" t="n">
         <v>269.5919503715612</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K57" t="n">
-        <v>0.91</v>
+        <v>-9.73</v>
       </c>
       <c r="L57" t="n">
-        <v>2.64</v>
+        <v>10.72</v>
       </c>
       <c r="M57" t="n">
         <v>0.02</v>
       </c>
       <c r="N57" t="n">
-        <v>3.16</v>
+        <v>10.74</v>
       </c>
       <c r="O57" t="n">
         <v>-2.54</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>14.94</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="H58" t="n">
-        <v>344.3</v>
+        <v>339.8</v>
       </c>
       <c r="I58" t="n">
         <v>340.1921708204208</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K58" t="n">
-        <v>23.65</v>
+        <v>22.03</v>
       </c>
       <c r="L58" t="n">
         <v>9.68</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>7</v>
+      </c>
+      <c r="U58" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H59" t="n">
-        <v>308.55</v>
+        <v>338.4</v>
       </c>
       <c r="I59" t="n">
         <v>334.0513203474794</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K59" t="n">
-        <v>9.199999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="L59" t="n">
         <v>6.19</v>
       </c>
       <c r="M59" t="n">
-        <v>4.49</v>
+        <v>4.91</v>
       </c>
       <c r="N59" t="n">
-        <v>4.38</v>
+        <v>9.67</v>
       </c>
       <c r="O59" t="n">
         <v>-1.31</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>15.58</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H60" t="n">
-        <v>395</v>
+        <v>378.8</v>
       </c>
       <c r="I60" t="n">
         <v>388.9138278591427</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K60" t="n">
-        <v>16.73</v>
+        <v>11.94</v>
       </c>
       <c r="L60" t="n">
         <v>5.14</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>6</v>
+      </c>
+      <c r="U60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="H61" t="n">
-        <v>390</v>
+        <v>410.05</v>
       </c>
       <c r="I61" t="n">
         <v>408.7314346481752</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.96</v>
+        <v>-8.25</v>
       </c>
       <c r="L61" t="n">
-        <v>4.75</v>
+        <v>8.25</v>
       </c>
       <c r="M61" t="n">
         <v>0.18</v>
       </c>
       <c r="N61" t="n">
-        <v>2.28</v>
+        <v>5.14</v>
       </c>
       <c r="O61" t="n">
         <v>-4.1</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>10</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="H62" t="n">
-        <v>378.9</v>
+        <v>372.1</v>
       </c>
       <c r="I62" t="n">
         <v>372.3677591414802</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K62" t="n">
-        <v>-7.6</v>
+        <v>-9.25</v>
       </c>
       <c r="L62" t="n">
-        <v>9.720000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="M62" t="n">
         <v>1.95</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,14 @@
       <c r="Q63" t="n">
         <v>15</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7905,7 +8668,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.5</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="6">
@@ -7915,7 +8678,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -7925,7 +8688,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8">
@@ -7935,7 +8698,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7945,7 +8708,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -7955,7 +8718,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -7965,7 +8728,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -7975,7 +8738,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -7985,7 +8748,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.3</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="14">
@@ -7995,7 +8758,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.99</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="15">
@@ -8005,7 +8768,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.58</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="16">
@@ -8015,7 +8778,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.34</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="17">
@@ -8025,7 +8788,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52.44</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="18">
@@ -8035,7 +8798,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.9</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="19">
@@ -8045,7 +8808,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.53</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -8055,7 +8818,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.89</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="21">
@@ -8065,7 +8828,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.36</v>
+        <v>22.19</v>
       </c>
     </row>
     <row r="22">
@@ -8075,7 +8838,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -8085,7 +8848,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -8095,7 +8858,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="25">
@@ -8115,7 +8878,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.47</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="27">
@@ -8125,7 +8888,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.380000000000001</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="28">
@@ -8135,7 +8898,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
